--- a/diplom/excel/график_2_конкуренты.xlsx
+++ b/diplom/excel/график_2_конкуренты.xlsx
@@ -27,6 +27,7 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -203,7 +204,10 @@
           </val>
         </ser>
         <dLbls>
+          <numFmt formatCode="#,##0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -224,14 +228,26 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Цена, ₽</a:t>
+                  <a:t>₽</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -242,23 +258,19 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Модель</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -277,7 +289,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="3960000"/>
+    <ext cx="7200000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -587,7 +599,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -606,7 +618,8 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ИП 103-5/4-А0 (тепловой)</t>
+          <t>ИП 103-5/4-А0
+(тепловой)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -616,7 +629,8 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ДИП-34ПА Болид (адресный дымовой)</t>
+          <t>ДИП-34ПА Болид
+(дымовой)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -626,7 +640,8 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ИП 212/101-4 ПРОФИ-ОТ (комбинированный)</t>
+          <t>ИП 212/101-4
+ПРОФИ-ОТ</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -636,7 +651,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>СигналПром (комбинированный)</t>
+          <t>СигналПром</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -646,7 +661,8 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ИП 212/101-18-A3R1 (премиум)</t>
+          <t>ИП 212/101-18
+(премиум)</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/diplom/excel/график_2_конкуренты.xlsx
+++ b/diplom/excel/график_2_конкуренты.xlsx
@@ -27,6 +27,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -39,12 +40,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +145,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
+  <style val="26"/>
   <chart>
     <title>
       <tx>
@@ -155,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сравнительный анализ отпускных цен пожарных извещателей</a:t>
+              <a:t>Сравнительный анализ отпускных цен извещателей</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -175,7 +176,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
+              <a:srgbClr val="A5A5A5"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -204,7 +205,7 @@
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="#,##0"/>
+          <numFmt formatCode="#,##0 ₽"/>
           <showVal val="1"/>
           <showCatName val="0"/>
           <showSerName val="0"/>
@@ -219,21 +220,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>₽</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -241,7 +227,7 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1000" b="0"/>
+              <a:defRPr sz="1100" b="0"/>
             </a:pPr>
             <a:r>
               <a:t/>
@@ -257,14 +243,13 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1000" b="0"/>
+              <a:defRPr sz="1100" b="0"/>
             </a:pPr>
             <a:r>
               <a:t/>
@@ -289,7 +274,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="4320000"/>
+    <ext cx="6480000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -599,7 +584,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -618,8 +603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ИП 103-5/4-А0
-(тепловой)</t>
+          <t>ИП 103-5/4-А0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -629,8 +613,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ДИП-34ПА Болид
-(дымовой)</t>
+          <t>ДИП-34ПА Болид</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -640,8 +623,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ИП 212/101-4
-ПРОФИ-ОТ</t>
+          <t>ПРОФИ-ОТ</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -661,8 +643,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ИП 212/101-18
-(премиум)</t>
+          <t>ИП 212/101-18</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/diplom/excel/график_2_конкуренты.xlsx
+++ b/diplom/excel/график_2_конкуренты.xlsx
@@ -145,7 +145,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="26"/>
   <chart>
     <title>
       <tx>
@@ -230,7 +229,7 @@
               <a:defRPr sz="1100" b="0"/>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -252,7 +251,7 @@
               <a:defRPr sz="1100" b="0"/>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -633,7 +632,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>СигналПром</t>
+          <t>ИПК «Сигнал»</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
